--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/02,07,26 ПОКОМ ЗПФ/дв 02,07,26 днрсч пок зпф.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/02,07,26 ПОКОМ ЗПФ/дв 02,07,26 днрсч пок зпф.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\02,07,26 ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B104F53-BB1F-4128-81D5-D7A1F524BE0B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57D387D-2DAE-4BC5-A068-53EEB3700893}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AI$69</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -6932,7 +6932,10 @@
         <f>SUM(AI6:AI500)</f>
         <v>34.928571428571431</v>
       </c>
-      <c r="AJ5" s="1"/>
+      <c r="AJ5" s="4">
+        <f>SUM(AJ6:AJ500)</f>
+        <v>2050.87</v>
+      </c>
       <c r="AK5" s="1"/>
       <c r="AL5" s="1"/>
       <c r="AM5" s="1"/>
@@ -7028,7 +7031,10 @@
       <c r="AG6" s="13"/>
       <c r="AH6" s="13"/>
       <c r="AI6" s="16"/>
-      <c r="AJ6" s="1"/>
+      <c r="AJ6" s="1">
+        <f>P6*G6</f>
+        <v>0</v>
+      </c>
       <c r="AK6" s="1"/>
       <c r="AL6" s="1"/>
       <c r="AM6" s="1"/>
@@ -7124,7 +7130,10 @@
       <c r="AG7" s="13"/>
       <c r="AH7" s="13"/>
       <c r="AI7" s="16"/>
-      <c r="AJ7" s="1"/>
+      <c r="AJ7" s="1">
+        <f t="shared" ref="AJ7:AJ69" si="6">P7*G7</f>
+        <v>0</v>
+      </c>
       <c r="AK7" s="1"/>
       <c r="AL7" s="1"/>
       <c r="AM7" s="1"/>
@@ -7212,7 +7221,10 @@
       <c r="AG8" s="13"/>
       <c r="AH8" s="13"/>
       <c r="AI8" s="16"/>
-      <c r="AJ8" s="1"/>
+      <c r="AJ8" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AK8" s="1"/>
       <c r="AL8" s="1"/>
       <c r="AM8" s="1"/>
@@ -7308,7 +7320,10 @@
       <c r="AG9" s="13"/>
       <c r="AH9" s="13"/>
       <c r="AI9" s="16"/>
-      <c r="AJ9" s="1"/>
+      <c r="AJ9" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AK9" s="1"/>
       <c r="AL9" s="1"/>
       <c r="AM9" s="1"/>
@@ -7377,7 +7392,7 @@
         <v>182.39999999999998</v>
       </c>
       <c r="R10" s="5">
-        <f t="shared" ref="R10:R18" si="6">AD10*AE10</f>
+        <f t="shared" ref="R10:R18" si="7">AD10*AE10</f>
         <v>168</v>
       </c>
       <c r="S10" s="25"/>
@@ -7409,7 +7424,7 @@
       </c>
       <c r="AB10" s="1"/>
       <c r="AC10" s="1">
-        <f t="shared" ref="AC10:AC18" si="7">G10*Q10</f>
+        <f t="shared" ref="AC10:AC18" si="8">G10*Q10</f>
         <v>54.719999999999992</v>
       </c>
       <c r="AD10" s="7">
@@ -7417,11 +7432,11 @@
         <v>12</v>
       </c>
       <c r="AE10" s="9">
-        <f t="shared" ref="AE10:AE18" si="8">MROUND(Q10, AD10*AG10)/AD10</f>
+        <f t="shared" ref="AE10:AE18" si="9">MROUND(Q10, AD10*AG10)/AD10</f>
         <v>14</v>
       </c>
       <c r="AF10" s="1">
-        <f t="shared" ref="AF10:AF18" si="9">AE10*AD10*G10</f>
+        <f t="shared" ref="AF10:AF18" si="10">AE10*AD10*G10</f>
         <v>50.4</v>
       </c>
       <c r="AG10" s="1">
@@ -7433,10 +7448,13 @@
         <v>70</v>
       </c>
       <c r="AI10" s="9">
-        <f t="shared" ref="AI10:AI18" si="10">AE10/AH10</f>
+        <f t="shared" ref="AI10:AI18" si="11">AE10/AH10</f>
         <v>0.2</v>
       </c>
-      <c r="AJ10" s="1"/>
+      <c r="AJ10" s="1">
+        <f t="shared" si="6"/>
+        <v>17.579999999999998</v>
+      </c>
       <c r="AK10" s="1"/>
       <c r="AL10" s="1"/>
       <c r="AM10" s="1"/>
@@ -7501,11 +7519,11 @@
         <v>78.599999999999994</v>
       </c>
       <c r="Q11" s="5">
-        <f t="shared" ref="Q11:Q16" si="11">14*P11-O11-F11</f>
+        <f t="shared" ref="Q11:Q16" si="12">14*P11-O11-F11</f>
         <v>251.39999999999986</v>
       </c>
       <c r="R11" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>252</v>
       </c>
       <c r="S11" s="25"/>
@@ -7537,7 +7555,7 @@
       </c>
       <c r="AB11" s="1"/>
       <c r="AC11" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>70.391999999999967</v>
       </c>
       <c r="AD11" s="7">
@@ -7545,11 +7563,11 @@
         <v>6</v>
       </c>
       <c r="AE11" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>42</v>
       </c>
       <c r="AF11" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>70.56</v>
       </c>
       <c r="AG11" s="1">
@@ -7561,10 +7579,13 @@
         <v>140</v>
       </c>
       <c r="AI11" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.3</v>
       </c>
-      <c r="AJ11" s="1"/>
+      <c r="AJ11" s="1">
+        <f t="shared" si="6"/>
+        <v>22.007999999999999</v>
+      </c>
       <c r="AK11" s="1"/>
       <c r="AL11" s="1"/>
       <c r="AM11" s="1"/>
@@ -7633,7 +7654,7 @@
         <v>595.72000000000025</v>
       </c>
       <c r="R12" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>672</v>
       </c>
       <c r="S12" s="25"/>
@@ -7665,7 +7686,7 @@
       </c>
       <c r="AB12" s="1"/>
       <c r="AC12" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>142.97280000000006</v>
       </c>
       <c r="AD12" s="7">
@@ -7673,11 +7694,11 @@
         <v>12</v>
       </c>
       <c r="AE12" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>56</v>
       </c>
       <c r="AF12" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>161.28</v>
       </c>
       <c r="AG12" s="1">
@@ -7689,10 +7710,13 @@
         <v>70</v>
       </c>
       <c r="AI12" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.8</v>
       </c>
-      <c r="AJ12" s="1"/>
+      <c r="AJ12" s="1">
+        <f t="shared" si="6"/>
+        <v>24.096</v>
+      </c>
       <c r="AK12" s="1"/>
       <c r="AL12" s="1"/>
       <c r="AM12" s="1"/>
@@ -7757,11 +7781,11 @@
         <v>197</v>
       </c>
       <c r="Q13" s="5">
-        <f t="shared" ref="Q13:Q15" si="12">$Q$1*P13-O13-F13</f>
+        <f t="shared" ref="Q13:Q14" si="13">$Q$1*P13-O13-F13</f>
         <v>1026.1000000000004</v>
       </c>
       <c r="R13" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1008</v>
       </c>
       <c r="S13" s="25"/>
@@ -7793,7 +7817,7 @@
       </c>
       <c r="AB13" s="1"/>
       <c r="AC13" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>246.26400000000007</v>
       </c>
       <c r="AD13" s="7">
@@ -7801,11 +7825,11 @@
         <v>12</v>
       </c>
       <c r="AE13" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>84</v>
       </c>
       <c r="AF13" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>241.92</v>
       </c>
       <c r="AG13" s="1">
@@ -7817,10 +7841,13 @@
         <v>70</v>
       </c>
       <c r="AI13" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.2</v>
       </c>
-      <c r="AJ13" s="1"/>
+      <c r="AJ13" s="1">
+        <f t="shared" si="6"/>
+        <v>47.28</v>
+      </c>
       <c r="AK13" s="1"/>
       <c r="AL13" s="1"/>
       <c r="AM13" s="1"/>
@@ -7885,11 +7912,11 @@
         <v>141</v>
       </c>
       <c r="Q14" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>902.30000000000018</v>
       </c>
       <c r="R14" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>840</v>
       </c>
       <c r="S14" s="25"/>
@@ -7921,7 +7948,7 @@
       </c>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>216.55200000000005</v>
       </c>
       <c r="AD14" s="7">
@@ -7929,11 +7956,11 @@
         <v>12</v>
       </c>
       <c r="AE14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>70</v>
       </c>
       <c r="AF14" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>201.6</v>
       </c>
       <c r="AG14" s="1">
@@ -7945,10 +7972,13 @@
         <v>70</v>
       </c>
       <c r="AI14" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="AJ14" s="1"/>
+      <c r="AJ14" s="1">
+        <f t="shared" si="6"/>
+        <v>33.839999999999996</v>
+      </c>
       <c r="AK14" s="1"/>
       <c r="AL14" s="1"/>
       <c r="AM14" s="1"/>
@@ -8019,7 +8049,7 @@
         <v>1908.96</v>
       </c>
       <c r="R15" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1848</v>
       </c>
       <c r="S15" s="25" t="s">
@@ -8055,7 +8085,7 @@
         <v>118</v>
       </c>
       <c r="AC15" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>458.15039999999999</v>
       </c>
       <c r="AD15" s="7">
@@ -8063,11 +8093,11 @@
         <v>12</v>
       </c>
       <c r="AE15" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>154</v>
       </c>
       <c r="AF15" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>443.52</v>
       </c>
       <c r="AG15" s="1">
@@ -8079,10 +8109,13 @@
         <v>70</v>
       </c>
       <c r="AI15" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="AJ15" s="1"/>
+      <c r="AJ15" s="1">
+        <f t="shared" si="6"/>
+        <v>35.327999999999996</v>
+      </c>
       <c r="AK15" s="1"/>
       <c r="AL15" s="1"/>
       <c r="AM15" s="1"/>
@@ -8147,11 +8180,11 @@
         <v>87</v>
       </c>
       <c r="Q16" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>196</v>
       </c>
       <c r="R16" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>224</v>
       </c>
       <c r="S16" s="25"/>
@@ -8183,7 +8216,7 @@
       </c>
       <c r="AB16" s="1"/>
       <c r="AC16" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>94.08</v>
       </c>
       <c r="AD16" s="7">
@@ -8191,11 +8224,11 @@
         <v>8</v>
       </c>
       <c r="AE16" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>28</v>
       </c>
       <c r="AF16" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>107.52</v>
       </c>
       <c r="AG16" s="1">
@@ -8207,10 +8240,13 @@
         <v>70</v>
       </c>
       <c r="AI16" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.4</v>
       </c>
-      <c r="AJ16" s="1"/>
+      <c r="AJ16" s="1">
+        <f t="shared" si="6"/>
+        <v>41.76</v>
+      </c>
       <c r="AK16" s="1"/>
       <c r="AL16" s="1"/>
       <c r="AM16" s="1"/>
@@ -8276,7 +8312,7 @@
       </c>
       <c r="Q17" s="5"/>
       <c r="R17" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S17" s="25"/>
@@ -8308,7 +8344,7 @@
       </c>
       <c r="AB17" s="1"/>
       <c r="AC17" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AD17" s="7">
@@ -8316,11 +8352,11 @@
         <v>24</v>
       </c>
       <c r="AE17" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AF17" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AG17" s="1">
@@ -8332,10 +8368,13 @@
         <v>126</v>
       </c>
       <c r="AI17" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AJ17" s="1"/>
+      <c r="AJ17" s="1">
+        <f t="shared" si="6"/>
+        <v>9.5939999999999994</v>
+      </c>
       <c r="AK17" s="1"/>
       <c r="AL17" s="1"/>
       <c r="AM17" s="1"/>
@@ -8404,7 +8443,7 @@
         <v>317.39999999999998</v>
       </c>
       <c r="R18" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>280</v>
       </c>
       <c r="S18" s="25"/>
@@ -8436,7 +8475,7 @@
       </c>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>114.26399999999998</v>
       </c>
       <c r="AD18" s="7">
@@ -8444,11 +8483,11 @@
         <v>10</v>
       </c>
       <c r="AE18" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>28</v>
       </c>
       <c r="AF18" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>100.8</v>
       </c>
       <c r="AG18" s="1">
@@ -8460,10 +8499,13 @@
         <v>70</v>
       </c>
       <c r="AI18" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.4</v>
       </c>
-      <c r="AJ18" s="1"/>
+      <c r="AJ18" s="1">
+        <f t="shared" si="6"/>
+        <v>11.807999999999998</v>
+      </c>
       <c r="AK18" s="1"/>
       <c r="AL18" s="1"/>
       <c r="AM18" s="1"/>
@@ -8559,7 +8601,10 @@
       <c r="AG19" s="13"/>
       <c r="AH19" s="13"/>
       <c r="AI19" s="16"/>
-      <c r="AJ19" s="1"/>
+      <c r="AJ19" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AK19" s="1"/>
       <c r="AL19" s="1"/>
       <c r="AM19" s="1"/>
@@ -8626,11 +8671,11 @@
         <v>84.6</v>
       </c>
       <c r="Q20" s="5">
-        <f t="shared" ref="Q20:Q28" si="13">14*P20-O20-F20</f>
+        <f t="shared" ref="Q20:Q28" si="14">14*P20-O20-F20</f>
         <v>631.39999999999986</v>
       </c>
       <c r="R20" s="5">
-        <f t="shared" ref="R20:R31" si="14">AD20*AE20</f>
+        <f t="shared" ref="R20:R31" si="15">AD20*AE20</f>
         <v>672</v>
       </c>
       <c r="S20" s="25"/>
@@ -8662,7 +8707,7 @@
       </c>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1">
-        <f t="shared" ref="AC20:AC31" si="15">G20*Q20</f>
+        <f t="shared" ref="AC20:AC31" si="16">G20*Q20</f>
         <v>126.27999999999997</v>
       </c>
       <c r="AD20" s="7">
@@ -8670,11 +8715,11 @@
         <v>12</v>
       </c>
       <c r="AE20" s="9">
-        <f t="shared" ref="AE20:AE31" si="16">MROUND(Q20, AD20*AG20)/AD20</f>
+        <f t="shared" ref="AE20:AE31" si="17">MROUND(Q20, AD20*AG20)/AD20</f>
         <v>56</v>
       </c>
       <c r="AF20" s="1">
-        <f t="shared" ref="AF20:AF31" si="17">AE20*AD20*G20</f>
+        <f t="shared" ref="AF20:AF31" si="18">AE20*AD20*G20</f>
         <v>134.4</v>
       </c>
       <c r="AG20" s="1">
@@ -8686,10 +8731,13 @@
         <v>70</v>
       </c>
       <c r="AI20" s="9">
-        <f t="shared" ref="AI20:AI31" si="18">AE20/AH20</f>
+        <f t="shared" ref="AI20:AI31" si="19">AE20/AH20</f>
         <v>0.8</v>
       </c>
-      <c r="AJ20" s="1"/>
+      <c r="AJ20" s="1">
+        <f t="shared" si="6"/>
+        <v>16.919999999999998</v>
+      </c>
       <c r="AK20" s="1"/>
       <c r="AL20" s="1"/>
       <c r="AM20" s="1"/>
@@ -8754,11 +8802,11 @@
         <v>182.2</v>
       </c>
       <c r="Q21" s="5">
-        <f t="shared" ref="Q21:Q22" si="19">$Q$1*P21-O21-F21</f>
+        <f t="shared" ref="Q21:Q22" si="20">$Q$1*P21-O21-F21</f>
         <v>903.46</v>
       </c>
       <c r="R21" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>840</v>
       </c>
       <c r="S21" s="25"/>
@@ -8790,7 +8838,7 @@
       </c>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>180.69200000000001</v>
       </c>
       <c r="AD21" s="7">
@@ -8798,11 +8846,11 @@
         <v>12</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>70</v>
       </c>
       <c r="AF21" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>168</v>
       </c>
       <c r="AG21" s="1">
@@ -8814,10 +8862,13 @@
         <v>70</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="AJ21" s="1"/>
+      <c r="AJ21" s="1">
+        <f t="shared" si="6"/>
+        <v>36.44</v>
+      </c>
       <c r="AK21" s="1"/>
       <c r="AL21" s="1"/>
       <c r="AM21" s="1"/>
@@ -8882,11 +8933,11 @@
         <v>116.4</v>
       </c>
       <c r="Q22" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1053.5200000000002</v>
       </c>
       <c r="R22" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1008</v>
       </c>
       <c r="S22" s="25"/>
@@ -8918,7 +8969,7 @@
       </c>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>210.70400000000006</v>
       </c>
       <c r="AD22" s="7">
@@ -8926,11 +8977,11 @@
         <v>12</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>84</v>
       </c>
       <c r="AF22" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>201.60000000000002</v>
       </c>
       <c r="AG22" s="1">
@@ -8942,10 +8993,13 @@
         <v>70</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.2</v>
       </c>
-      <c r="AJ22" s="1"/>
+      <c r="AJ22" s="1">
+        <f t="shared" si="6"/>
+        <v>23.28</v>
+      </c>
       <c r="AK22" s="1"/>
       <c r="AL22" s="1"/>
       <c r="AM22" s="1"/>
@@ -9010,11 +9064,11 @@
         <v>53</v>
       </c>
       <c r="Q23" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>344</v>
       </c>
       <c r="R23" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>360</v>
       </c>
       <c r="S23" s="25"/>
@@ -9046,7 +9100,7 @@
       </c>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>344</v>
       </c>
       <c r="AD23" s="7">
@@ -9054,11 +9108,11 @@
         <v>5</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>72</v>
       </c>
       <c r="AF23" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>360</v>
       </c>
       <c r="AG23" s="1">
@@ -9070,10 +9124,13 @@
         <v>84</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.8571428571428571</v>
       </c>
-      <c r="AJ23" s="1"/>
+      <c r="AJ23" s="1">
+        <f t="shared" si="6"/>
+        <v>53</v>
+      </c>
       <c r="AK23" s="1"/>
       <c r="AL23" s="1"/>
       <c r="AM23" s="1"/>
@@ -9136,7 +9193,7 @@
       </c>
       <c r="Q24" s="5"/>
       <c r="R24" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="S24" s="25"/>
@@ -9168,20 +9225,20 @@
       </c>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AD24" s="7">
         <v>5.5</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AF24" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
+      <c r="AF24" s="1">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
       <c r="AG24" s="1">
         <v>12</v>
       </c>
@@ -9189,10 +9246,13 @@
         <v>84</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AJ24" s="7"/>
+      <c r="AJ24" s="1">
+        <f t="shared" si="6"/>
+        <v>27.3</v>
+      </c>
       <c r="AK24" s="1"/>
       <c r="AL24" s="1"/>
       <c r="AM24" s="1"/>
@@ -9257,11 +9317,11 @@
         <v>37</v>
       </c>
       <c r="Q25" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>90</v>
       </c>
       <c r="R25" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>84</v>
       </c>
       <c r="S25" s="25"/>
@@ -9293,7 +9353,7 @@
       </c>
       <c r="AB25" s="1"/>
       <c r="AC25" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>90</v>
       </c>
       <c r="AD25" s="7">
@@ -9301,11 +9361,11 @@
         <v>3</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>28</v>
       </c>
       <c r="AF25" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>84</v>
       </c>
       <c r="AG25" s="1">
@@ -9317,10 +9377,13 @@
         <v>126</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.22222222222222221</v>
       </c>
-      <c r="AJ25" s="1"/>
+      <c r="AJ25" s="1">
+        <f t="shared" si="6"/>
+        <v>37</v>
+      </c>
       <c r="AK25" s="1"/>
       <c r="AL25" s="1"/>
       <c r="AM25" s="1"/>
@@ -9389,7 +9452,7 @@
         <v>1115.78</v>
       </c>
       <c r="R26" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1092</v>
       </c>
       <c r="S26" s="25"/>
@@ -9421,7 +9484,7 @@
       </c>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>278.94499999999999</v>
       </c>
       <c r="AD26" s="7">
@@ -9429,11 +9492,11 @@
         <v>6</v>
       </c>
       <c r="AE26" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>182</v>
       </c>
       <c r="AF26" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>273</v>
       </c>
       <c r="AG26" s="1">
@@ -9445,10 +9508,13 @@
         <v>140</v>
       </c>
       <c r="AI26" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.3</v>
       </c>
-      <c r="AJ26" s="1"/>
+      <c r="AJ26" s="1">
+        <f t="shared" si="6"/>
+        <v>28.65</v>
+      </c>
       <c r="AK26" s="1"/>
       <c r="AL26" s="1"/>
       <c r="AM26" s="1"/>
@@ -9513,11 +9579,11 @@
         <v>92.8</v>
       </c>
       <c r="Q27" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>649.20000000000005</v>
       </c>
       <c r="R27" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>672</v>
       </c>
       <c r="S27" s="25"/>
@@ -9549,7 +9615,7 @@
       </c>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>162.30000000000001</v>
       </c>
       <c r="AD27" s="7">
@@ -9557,11 +9623,11 @@
         <v>6</v>
       </c>
       <c r="AE27" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>112</v>
       </c>
       <c r="AF27" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>168</v>
       </c>
       <c r="AG27" s="1">
@@ -9573,10 +9639,13 @@
         <v>140</v>
       </c>
       <c r="AI27" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.8</v>
       </c>
-      <c r="AJ27" s="1"/>
+      <c r="AJ27" s="1">
+        <f t="shared" si="6"/>
+        <v>23.2</v>
+      </c>
       <c r="AK27" s="1"/>
       <c r="AL27" s="1"/>
       <c r="AM27" s="1"/>
@@ -9641,11 +9710,11 @@
         <v>58.6</v>
       </c>
       <c r="Q28" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>148.39999999999998</v>
       </c>
       <c r="R28" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>144</v>
       </c>
       <c r="S28" s="25"/>
@@ -9677,7 +9746,7 @@
       </c>
       <c r="AB28" s="1"/>
       <c r="AC28" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>148.39999999999998</v>
       </c>
       <c r="AD28" s="7">
@@ -9685,11 +9754,11 @@
         <v>6</v>
       </c>
       <c r="AE28" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>24</v>
       </c>
       <c r="AF28" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>144</v>
       </c>
       <c r="AG28" s="1">
@@ -9701,10 +9770,13 @@
         <v>84</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="AJ28" s="1"/>
+      <c r="AJ28" s="1">
+        <f t="shared" si="6"/>
+        <v>58.6</v>
+      </c>
       <c r="AK28" s="1"/>
       <c r="AL28" s="1"/>
       <c r="AM28" s="1"/>
@@ -9769,7 +9841,7 @@
       </c>
       <c r="Q29" s="5"/>
       <c r="R29" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="S29" s="25"/>
@@ -9803,7 +9875,7 @@
         <v>69</v>
       </c>
       <c r="AC29" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AD29" s="7">
@@ -9811,11 +9883,11 @@
         <v>12</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF29" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AG29" s="1">
@@ -9827,10 +9899,13 @@
         <v>70</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AJ29" s="1"/>
+      <c r="AJ29" s="1">
+        <f t="shared" si="6"/>
+        <v>17.204000000000001</v>
+      </c>
       <c r="AK29" s="1"/>
       <c r="AL29" s="1"/>
       <c r="AM29" s="1"/>
@@ -9895,11 +9970,11 @@
         <v>185.6</v>
       </c>
       <c r="Q30" s="5">
-        <f t="shared" ref="Q30:Q31" si="20">$Q$1*P30-O30-F30</f>
+        <f t="shared" ref="Q30:Q31" si="21">$Q$1*P30-O30-F30</f>
         <v>1046.08</v>
       </c>
       <c r="R30" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1008</v>
       </c>
       <c r="S30" s="25"/>
@@ -9931,7 +10006,7 @@
       </c>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>261.52</v>
       </c>
       <c r="AD30" s="7">
@@ -9939,11 +10014,11 @@
         <v>12</v>
       </c>
       <c r="AE30" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>84</v>
       </c>
       <c r="AF30" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>252</v>
       </c>
       <c r="AG30" s="1">
@@ -9955,10 +10030,13 @@
         <v>70</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.2</v>
       </c>
-      <c r="AJ30" s="1"/>
+      <c r="AJ30" s="1">
+        <f t="shared" si="6"/>
+        <v>46.4</v>
+      </c>
       <c r="AK30" s="1"/>
       <c r="AL30" s="1"/>
       <c r="AM30" s="1"/>
@@ -10023,11 +10101,11 @@
         <v>147.80000000000001</v>
       </c>
       <c r="Q31" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>923.54000000000042</v>
       </c>
       <c r="R31" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>840</v>
       </c>
       <c r="S31" s="25"/>
@@ -10059,7 +10137,7 @@
       </c>
       <c r="AB31" s="1"/>
       <c r="AC31" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>230.8850000000001</v>
       </c>
       <c r="AD31" s="7">
@@ -10067,11 +10145,11 @@
         <v>12</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>70</v>
       </c>
       <c r="AF31" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>210</v>
       </c>
       <c r="AG31" s="1">
@@ -10083,10 +10161,13 @@
         <v>70</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="AJ31" s="1"/>
+      <c r="AJ31" s="1">
+        <f t="shared" si="6"/>
+        <v>36.950000000000003</v>
+      </c>
       <c r="AK31" s="1"/>
       <c r="AL31" s="1"/>
       <c r="AM31" s="1"/>
@@ -10175,7 +10256,10 @@
       <c r="AG32" s="13"/>
       <c r="AH32" s="13"/>
       <c r="AI32" s="16"/>
-      <c r="AJ32" s="1"/>
+      <c r="AJ32" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AK32" s="1"/>
       <c r="AL32" s="1"/>
       <c r="AM32" s="1"/>
@@ -10244,7 +10328,7 @@
         <v>535.54</v>
       </c>
       <c r="R33" s="5">
-        <f t="shared" ref="R33:R49" si="21">AD33*AE33</f>
+        <f t="shared" ref="R33:R49" si="22">AD33*AE33</f>
         <v>504</v>
       </c>
       <c r="S33" s="25"/>
@@ -10276,7 +10360,7 @@
       </c>
       <c r="AB33" s="1"/>
       <c r="AC33" s="1">
-        <f t="shared" ref="AC33:AC49" si="22">G33*Q33</f>
+        <f t="shared" ref="AC33:AC49" si="23">G33*Q33</f>
         <v>133.88499999999999</v>
       </c>
       <c r="AD33" s="7">
@@ -10284,11 +10368,11 @@
         <v>12</v>
       </c>
       <c r="AE33" s="9">
-        <f t="shared" ref="AE33:AE49" si="23">MROUND(Q33, AD33*AG33)/AD33</f>
+        <f t="shared" ref="AE33:AE49" si="24">MROUND(Q33, AD33*AG33)/AD33</f>
         <v>42</v>
       </c>
       <c r="AF33" s="1">
-        <f t="shared" ref="AF33:AF49" si="24">AE33*AD33*G33</f>
+        <f t="shared" ref="AF33:AF49" si="25">AE33*AD33*G33</f>
         <v>126</v>
       </c>
       <c r="AG33" s="1">
@@ -10300,10 +10384,13 @@
         <v>70</v>
       </c>
       <c r="AI33" s="9">
-        <f t="shared" ref="AI33:AI49" si="25">AE33/AH33</f>
+        <f t="shared" ref="AI33:AI49" si="26">AE33/AH33</f>
         <v>0.6</v>
       </c>
-      <c r="AJ33" s="1"/>
+      <c r="AJ33" s="1">
+        <f t="shared" si="6"/>
+        <v>29.45</v>
+      </c>
       <c r="AK33" s="1"/>
       <c r="AL33" s="1"/>
       <c r="AM33" s="1"/>
@@ -10368,11 +10455,11 @@
         <v>61.4</v>
       </c>
       <c r="Q34" s="5">
-        <f t="shared" ref="Q34:Q46" si="26">14*P34-O34-F34</f>
+        <f t="shared" ref="Q34:Q46" si="27">14*P34-O34-F34</f>
         <v>482.6</v>
       </c>
       <c r="R34" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>504</v>
       </c>
       <c r="S34" s="25"/>
@@ -10404,7 +10491,7 @@
       </c>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>120.65</v>
       </c>
       <c r="AD34" s="7">
@@ -10412,11 +10499,11 @@
         <v>12</v>
       </c>
       <c r="AE34" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>42</v>
       </c>
       <c r="AF34" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>126</v>
       </c>
       <c r="AG34" s="1">
@@ -10428,10 +10515,13 @@
         <v>70</v>
       </c>
       <c r="AI34" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.6</v>
       </c>
-      <c r="AJ34" s="1"/>
+      <c r="AJ34" s="1">
+        <f t="shared" si="6"/>
+        <v>15.35</v>
+      </c>
       <c r="AK34" s="1"/>
       <c r="AL34" s="1"/>
       <c r="AM34" s="1"/>
@@ -10496,11 +10586,11 @@
         <v>57.4</v>
       </c>
       <c r="Q35" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>411.6</v>
       </c>
       <c r="R35" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>384</v>
       </c>
       <c r="S35" s="25"/>
@@ -10532,7 +10622,7 @@
       </c>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>288.12</v>
       </c>
       <c r="AD35" s="7">
@@ -10540,11 +10630,11 @@
         <v>8</v>
       </c>
       <c r="AE35" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>48</v>
       </c>
       <c r="AF35" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>268.79999999999995</v>
       </c>
       <c r="AG35" s="1">
@@ -10556,10 +10646,13 @@
         <v>84</v>
       </c>
       <c r="AI35" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.5714285714285714</v>
       </c>
-      <c r="AJ35" s="1"/>
+      <c r="AJ35" s="1">
+        <f t="shared" si="6"/>
+        <v>40.18</v>
+      </c>
       <c r="AK35" s="1"/>
       <c r="AL35" s="1"/>
       <c r="AM35" s="1"/>
@@ -10624,11 +10717,11 @@
         <v>41.4</v>
       </c>
       <c r="Q36" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>208.60000000000002</v>
       </c>
       <c r="R36" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>192</v>
       </c>
       <c r="S36" s="25"/>
@@ -10660,7 +10753,7 @@
       </c>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>146.02000000000001</v>
       </c>
       <c r="AD36" s="7">
@@ -10668,11 +10761,11 @@
         <v>8</v>
       </c>
       <c r="AE36" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>24</v>
       </c>
       <c r="AF36" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>134.39999999999998</v>
       </c>
       <c r="AG36" s="1">
@@ -10684,10 +10777,13 @@
         <v>84</v>
       </c>
       <c r="AI36" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="AJ36" s="1"/>
+      <c r="AJ36" s="1">
+        <f t="shared" si="6"/>
+        <v>28.979999999999997</v>
+      </c>
       <c r="AK36" s="1"/>
       <c r="AL36" s="1"/>
       <c r="AM36" s="1"/>
@@ -10752,11 +10848,11 @@
         <v>68.400000000000006</v>
       </c>
       <c r="Q37" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>330.60000000000014</v>
       </c>
       <c r="R37" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>288</v>
       </c>
       <c r="S37" s="25"/>
@@ -10788,7 +10884,7 @@
       </c>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>231.42000000000007</v>
       </c>
       <c r="AD37" s="7">
@@ -10796,11 +10892,11 @@
         <v>8</v>
       </c>
       <c r="AE37" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>36</v>
       </c>
       <c r="AF37" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>201.6</v>
       </c>
       <c r="AG37" s="1">
@@ -10812,10 +10908,13 @@
         <v>84</v>
       </c>
       <c r="AI37" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="AJ37" s="1"/>
+      <c r="AJ37" s="1">
+        <f t="shared" si="6"/>
+        <v>47.88</v>
+      </c>
       <c r="AK37" s="1"/>
       <c r="AL37" s="1"/>
       <c r="AM37" s="1"/>
@@ -10867,7 +10966,7 @@
         <v>386</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="27">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="28">E38-K38</f>
         <v>-21</v>
       </c>
       <c r="M38" s="1"/>
@@ -10876,7 +10975,7 @@
         <v>120</v>
       </c>
       <c r="P38" s="1">
-        <f t="shared" ref="P38:P69" si="28">E38/5</f>
+        <f t="shared" ref="P38:P69" si="29">E38/5</f>
         <v>73</v>
       </c>
       <c r="Q38" s="5">
@@ -10884,18 +10983,18 @@
         <v>1745</v>
       </c>
       <c r="R38" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1800</v>
       </c>
       <c r="S38" s="25" t="s">
         <v>117</v>
       </c>
       <c r="T38" s="1">
-        <f t="shared" ref="T38:T69" si="29">(F38+O38+R38)/P38</f>
+        <f t="shared" ref="T38:T69" si="30">(F38+O38+R38)/P38</f>
         <v>26.452054794520549</v>
       </c>
       <c r="U38" s="1">
-        <f t="shared" ref="U38:U69" si="30">(F38+O38)/P38</f>
+        <f t="shared" ref="U38:U69" si="31">(F38+O38)/P38</f>
         <v>1.7945205479452055</v>
       </c>
       <c r="V38" s="1">
@@ -10920,7 +11019,7 @@
         <v>118</v>
       </c>
       <c r="AC38" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1221.5</v>
       </c>
       <c r="AD38" s="7">
@@ -10928,11 +11027,11 @@
         <v>10</v>
       </c>
       <c r="AE38" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>180</v>
       </c>
       <c r="AF38" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1260</v>
       </c>
       <c r="AG38" s="1">
@@ -10944,10 +11043,13 @@
         <v>84</v>
       </c>
       <c r="AI38" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>2.1428571428571428</v>
       </c>
-      <c r="AJ38" s="1"/>
+      <c r="AJ38" s="1">
+        <f t="shared" si="6"/>
+        <v>51.099999999999994</v>
+      </c>
       <c r="AK38" s="1"/>
       <c r="AL38" s="1"/>
       <c r="AM38" s="1"/>
@@ -10997,7 +11099,7 @@
         <v>277</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-182</v>
       </c>
       <c r="M39" s="1"/>
@@ -11006,23 +11108,23 @@
         <v>576</v>
       </c>
       <c r="P39" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>19</v>
       </c>
       <c r="Q39" s="5"/>
       <c r="R39" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="S39" s="25"/>
       <c r="T39" s="1">
-        <f t="shared" si="29"/>
-        <v>30.315789473684209</v>
-      </c>
-      <c r="U39" s="1">
         <f t="shared" si="30"/>
         <v>30.315789473684209</v>
       </c>
+      <c r="U39" s="1">
+        <f t="shared" si="31"/>
+        <v>30.315789473684209</v>
+      </c>
       <c r="V39" s="1">
         <v>103.4</v>
       </c>
@@ -11043,7 +11145,7 @@
       </c>
       <c r="AB39" s="1"/>
       <c r="AC39" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AD39" s="7">
@@ -11051,11 +11153,11 @@
         <v>10</v>
       </c>
       <c r="AE39" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AF39" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AG39" s="1">
@@ -11067,10 +11169,13 @@
         <v>84</v>
       </c>
       <c r="AI39" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AJ39" s="1"/>
+      <c r="AJ39" s="1">
+        <f t="shared" si="6"/>
+        <v>13.299999999999999</v>
+      </c>
       <c r="AK39" s="1"/>
       <c r="AL39" s="1"/>
       <c r="AM39" s="1"/>
@@ -11119,7 +11224,7 @@
         <v>293</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-156</v>
       </c>
       <c r="M40" s="1"/>
@@ -11128,23 +11233,23 @@
         <v>576</v>
       </c>
       <c r="P40" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>27.4</v>
       </c>
       <c r="Q40" s="5"/>
       <c r="R40" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="S40" s="25"/>
       <c r="T40" s="1">
-        <f t="shared" si="29"/>
-        <v>22.372262773722628</v>
-      </c>
-      <c r="U40" s="1">
         <f t="shared" si="30"/>
         <v>22.372262773722628</v>
       </c>
+      <c r="U40" s="1">
+        <f t="shared" si="31"/>
+        <v>22.372262773722628</v>
+      </c>
       <c r="V40" s="1">
         <v>85.8</v>
       </c>
@@ -11165,20 +11270,20 @@
       </c>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AD40" s="1">
         <v>16</v>
       </c>
       <c r="AE40" s="9">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AF40" s="1">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
+      <c r="AF40" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AG40" s="1">
         <v>12</v>
       </c>
@@ -11186,10 +11291,13 @@
         <v>84</v>
       </c>
       <c r="AI40" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AJ40" s="1"/>
+      <c r="AJ40" s="1">
+        <f t="shared" si="6"/>
+        <v>10.96</v>
+      </c>
       <c r="AK40" s="1"/>
       <c r="AL40" s="1"/>
       <c r="AM40" s="1"/>
@@ -11241,7 +11349,7 @@
         <v>474</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-163</v>
       </c>
       <c r="M41" s="1"/>
@@ -11250,24 +11358,24 @@
         <v>480</v>
       </c>
       <c r="P41" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>62.2</v>
       </c>
       <c r="Q41" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>384.80000000000007</v>
       </c>
       <c r="R41" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>360</v>
       </c>
       <c r="S41" s="25"/>
       <c r="T41" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>13.60128617363344</v>
       </c>
       <c r="U41" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>7.813504823151125</v>
       </c>
       <c r="V41" s="1">
@@ -11290,7 +11398,7 @@
       </c>
       <c r="AB41" s="1"/>
       <c r="AC41" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>269.36</v>
       </c>
       <c r="AD41" s="7">
@@ -11298,11 +11406,11 @@
         <v>10</v>
       </c>
       <c r="AE41" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>36</v>
       </c>
       <c r="AF41" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>251.99999999999997</v>
       </c>
       <c r="AG41" s="1">
@@ -11314,10 +11422,13 @@
         <v>84</v>
       </c>
       <c r="AI41" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="AJ41" s="1"/>
+      <c r="AJ41" s="1">
+        <f t="shared" si="6"/>
+        <v>43.54</v>
+      </c>
       <c r="AK41" s="1"/>
       <c r="AL41" s="1"/>
       <c r="AM41" s="1"/>
@@ -11369,7 +11480,7 @@
         <v>512</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-36</v>
       </c>
       <c r="M42" s="1"/>
@@ -11378,24 +11489,24 @@
         <v>840</v>
       </c>
       <c r="P42" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>95.2</v>
       </c>
       <c r="Q42" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>301.79999999999995</v>
       </c>
       <c r="R42" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>360</v>
       </c>
       <c r="S42" s="25"/>
       <c r="T42" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>14.611344537815125</v>
       </c>
       <c r="U42" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>10.829831932773109</v>
       </c>
       <c r="V42" s="1">
@@ -11418,7 +11529,7 @@
       </c>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>211.25999999999996</v>
       </c>
       <c r="AD42" s="7">
@@ -11426,11 +11537,11 @@
         <v>10</v>
       </c>
       <c r="AE42" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>36</v>
       </c>
       <c r="AF42" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>251.99999999999997</v>
       </c>
       <c r="AG42" s="1">
@@ -11442,10 +11553,13 @@
         <v>84</v>
       </c>
       <c r="AI42" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="AJ42" s="1"/>
+      <c r="AJ42" s="1">
+        <f t="shared" si="6"/>
+        <v>66.64</v>
+      </c>
       <c r="AK42" s="1"/>
       <c r="AL42" s="1"/>
       <c r="AM42" s="1"/>
@@ -11497,7 +11611,7 @@
         <v>515</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-35</v>
       </c>
       <c r="M43" s="1"/>
@@ -11506,24 +11620,24 @@
         <v>420</v>
       </c>
       <c r="P43" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>96</v>
       </c>
       <c r="Q43" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>644</v>
       </c>
       <c r="R43" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>660</v>
       </c>
       <c r="S43" s="25"/>
       <c r="T43" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>14.166666666666666</v>
       </c>
       <c r="U43" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>7.291666666666667</v>
       </c>
       <c r="V43" s="1">
@@ -11546,7 +11660,7 @@
       </c>
       <c r="AB43" s="1"/>
       <c r="AC43" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>644</v>
       </c>
       <c r="AD43" s="7">
@@ -11554,11 +11668,11 @@
         <v>5</v>
       </c>
       <c r="AE43" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>132</v>
       </c>
       <c r="AF43" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>660</v>
       </c>
       <c r="AG43" s="1">
@@ -11570,10 +11684,13 @@
         <v>144</v>
       </c>
       <c r="AI43" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.91666666666666663</v>
       </c>
-      <c r="AJ43" s="1"/>
+      <c r="AJ43" s="1">
+        <f t="shared" si="6"/>
+        <v>96</v>
+      </c>
       <c r="AK43" s="1"/>
       <c r="AL43" s="1"/>
       <c r="AM43" s="1"/>
@@ -11625,7 +11742,7 @@
         <v>319</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-34</v>
       </c>
       <c r="M44" s="1"/>
@@ -11634,23 +11751,23 @@
         <v>0</v>
       </c>
       <c r="P44" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>57</v>
       </c>
       <c r="Q44" s="5"/>
       <c r="R44" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="S44" s="25"/>
       <c r="T44" s="1">
-        <f t="shared" si="29"/>
-        <v>48.964912280701753</v>
-      </c>
-      <c r="U44" s="1">
         <f t="shared" si="30"/>
         <v>48.964912280701753</v>
       </c>
+      <c r="U44" s="1">
+        <f t="shared" si="31"/>
+        <v>48.964912280701753</v>
+      </c>
       <c r="V44" s="1">
         <v>69</v>
       </c>
@@ -11673,7 +11790,7 @@
         <v>90</v>
       </c>
       <c r="AC44" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AD44" s="7">
@@ -11681,11 +11798,11 @@
         <v>16</v>
       </c>
       <c r="AE44" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AF44" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AG44" s="1">
@@ -11697,10 +11814,13 @@
         <v>84</v>
       </c>
       <c r="AI44" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AJ44" s="1"/>
+      <c r="AJ44" s="1">
+        <f t="shared" si="6"/>
+        <v>22.8</v>
+      </c>
       <c r="AK44" s="1"/>
       <c r="AL44" s="1"/>
       <c r="AM44" s="1"/>
@@ -11752,7 +11872,7 @@
         <v>672</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-56</v>
       </c>
       <c r="M45" s="1"/>
@@ -11761,7 +11881,7 @@
         <v>600</v>
       </c>
       <c r="P45" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>123.2</v>
       </c>
       <c r="Q45" s="5">
@@ -11769,16 +11889,16 @@
         <v>993.76000000000022</v>
       </c>
       <c r="R45" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>960</v>
       </c>
       <c r="S45" s="25"/>
       <c r="T45" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>14.025974025974026</v>
       </c>
       <c r="U45" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>6.2337662337662341</v>
       </c>
       <c r="V45" s="1">
@@ -11801,7 +11921,7 @@
       </c>
       <c r="AB45" s="1"/>
       <c r="AC45" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>695.63200000000006</v>
       </c>
       <c r="AD45" s="7">
@@ -11809,11 +11929,11 @@
         <v>10</v>
       </c>
       <c r="AE45" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>96</v>
       </c>
       <c r="AF45" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>672</v>
       </c>
       <c r="AG45" s="1">
@@ -11825,10 +11945,13 @@
         <v>84</v>
       </c>
       <c r="AI45" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1.1428571428571428</v>
       </c>
-      <c r="AJ45" s="1"/>
+      <c r="AJ45" s="1">
+        <f t="shared" si="6"/>
+        <v>86.24</v>
+      </c>
       <c r="AK45" s="1"/>
       <c r="AL45" s="1"/>
       <c r="AM45" s="1"/>
@@ -11880,7 +12003,7 @@
         <v>267</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-53</v>
       </c>
       <c r="M46" s="1"/>
@@ -11889,24 +12012,24 @@
         <v>0</v>
       </c>
       <c r="P46" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>42.8</v>
       </c>
       <c r="Q46" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>366.19999999999993</v>
       </c>
       <c r="R46" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>384</v>
       </c>
       <c r="S46" s="25"/>
       <c r="T46" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>14.415887850467291</v>
       </c>
       <c r="U46" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>5.44392523364486</v>
       </c>
       <c r="V46" s="1">
@@ -11929,7 +12052,7 @@
       </c>
       <c r="AB46" s="1"/>
       <c r="AC46" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>146.47999999999999</v>
       </c>
       <c r="AD46" s="7">
@@ -11937,11 +12060,11 @@
         <v>16</v>
       </c>
       <c r="AE46" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>24</v>
       </c>
       <c r="AF46" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>153.60000000000002</v>
       </c>
       <c r="AG46" s="1">
@@ -11953,10 +12076,13 @@
         <v>84</v>
       </c>
       <c r="AI46" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="AJ46" s="1"/>
+      <c r="AJ46" s="1">
+        <f t="shared" si="6"/>
+        <v>17.12</v>
+      </c>
       <c r="AK46" s="1"/>
       <c r="AL46" s="1"/>
       <c r="AM46" s="1"/>
@@ -12010,7 +12136,7 @@
         <v>867</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>65</v>
       </c>
       <c r="M47" s="1"/>
@@ -12019,24 +12145,24 @@
         <v>840</v>
       </c>
       <c r="P47" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>186.4</v>
       </c>
       <c r="Q47" s="5">
-        <f t="shared" ref="Q47:Q48" si="31">$Q$1*P47-O47-F47</f>
+        <f t="shared" ref="Q47:Q48" si="32">$Q$1*P47-O47-F47</f>
         <v>975.52000000000044</v>
       </c>
       <c r="R47" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>960</v>
       </c>
       <c r="S47" s="25"/>
       <c r="T47" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>14.216738197424892</v>
       </c>
       <c r="U47" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9.0665236051502145</v>
       </c>
       <c r="V47" s="1">
@@ -12059,7 +12185,7 @@
       </c>
       <c r="AB47" s="1"/>
       <c r="AC47" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>682.86400000000026</v>
       </c>
       <c r="AD47" s="7">
@@ -12067,11 +12193,11 @@
         <v>10</v>
       </c>
       <c r="AE47" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>96</v>
       </c>
       <c r="AF47" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>672</v>
       </c>
       <c r="AG47" s="1">
@@ -12083,10 +12209,13 @@
         <v>84</v>
       </c>
       <c r="AI47" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1.1428571428571428</v>
       </c>
-      <c r="AJ47" s="1"/>
+      <c r="AJ47" s="1">
+        <f t="shared" si="6"/>
+        <v>130.47999999999999</v>
+      </c>
       <c r="AK47" s="1"/>
       <c r="AL47" s="1"/>
       <c r="AM47" s="1"/>
@@ -12138,7 +12267,7 @@
         <v>708</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-32</v>
       </c>
       <c r="M48" s="1"/>
@@ -12147,24 +12276,24 @@
         <v>660</v>
       </c>
       <c r="P48" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>135.19999999999999</v>
       </c>
       <c r="Q48" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>637.3599999999999</v>
       </c>
       <c r="R48" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>660</v>
       </c>
       <c r="S48" s="25"/>
       <c r="T48" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>14.467455621301776</v>
       </c>
       <c r="U48" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9.5857988165680474</v>
       </c>
       <c r="V48" s="1">
@@ -12187,7 +12316,7 @@
       </c>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>637.3599999999999</v>
       </c>
       <c r="AD48" s="7">
@@ -12195,11 +12324,11 @@
         <v>5</v>
       </c>
       <c r="AE48" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>132</v>
       </c>
       <c r="AF48" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>660</v>
       </c>
       <c r="AG48" s="1">
@@ -12211,10 +12340,13 @@
         <v>84</v>
       </c>
       <c r="AI48" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AJ48" s="1"/>
+      <c r="AJ48" s="1">
+        <f t="shared" si="6"/>
+        <v>135.19999999999999</v>
+      </c>
       <c r="AK48" s="1"/>
       <c r="AL48" s="1"/>
       <c r="AM48" s="1"/>
@@ -12266,7 +12398,7 @@
         <v>165</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-2</v>
       </c>
       <c r="M49" s="1"/>
@@ -12275,7 +12407,7 @@
         <v>0</v>
       </c>
       <c r="P49" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>32.6</v>
       </c>
       <c r="Q49" s="5">
@@ -12283,16 +12415,16 @@
         <v>256.20000000000005</v>
       </c>
       <c r="R49" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>288</v>
       </c>
       <c r="S49" s="25"/>
       <c r="T49" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>12.975460122699387</v>
       </c>
       <c r="U49" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>4.1411042944785272</v>
       </c>
       <c r="V49" s="1">
@@ -12315,7 +12447,7 @@
       </c>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>230.58000000000004</v>
       </c>
       <c r="AD49" s="7">
@@ -12323,11 +12455,11 @@
         <v>8</v>
       </c>
       <c r="AE49" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>36</v>
       </c>
       <c r="AF49" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>259.2</v>
       </c>
       <c r="AG49" s="1">
@@ -12339,10 +12471,13 @@
         <v>84</v>
       </c>
       <c r="AI49" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="AJ49" s="1"/>
+      <c r="AJ49" s="1">
+        <f t="shared" si="6"/>
+        <v>29.340000000000003</v>
+      </c>
       <c r="AK49" s="1"/>
       <c r="AL49" s="1"/>
       <c r="AM49" s="1"/>
@@ -12387,25 +12522,25 @@
         <v>3</v>
       </c>
       <c r="L50" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M50" s="13"/>
       <c r="N50" s="13"/>
       <c r="O50" s="13"/>
       <c r="P50" s="13">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.6</v>
       </c>
       <c r="Q50" s="15"/>
       <c r="R50" s="15"/>
       <c r="S50" s="24"/>
       <c r="T50" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-1.6666666666666667</v>
       </c>
       <c r="U50" s="13">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-1.6666666666666667</v>
       </c>
       <c r="V50" s="13">
@@ -12434,7 +12569,10 @@
       <c r="AG50" s="13"/>
       <c r="AH50" s="13"/>
       <c r="AI50" s="16"/>
-      <c r="AJ50" s="1"/>
+      <c r="AJ50" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AK50" s="1"/>
       <c r="AL50" s="1"/>
       <c r="AM50" s="1"/>
@@ -12486,7 +12624,7 @@
         <v>405</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-140</v>
       </c>
       <c r="M51" s="1"/>
@@ -12495,24 +12633,24 @@
         <v>420</v>
       </c>
       <c r="P51" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>53</v>
       </c>
       <c r="Q51" s="5">
-        <f t="shared" ref="Q51:Q68" si="32">14*P51-O51-F51</f>
+        <f t="shared" ref="Q51:Q68" si="33">14*P51-O51-F51</f>
         <v>302</v>
       </c>
       <c r="R51" s="5">
-        <f t="shared" ref="R51:R70" si="33">AD51*AE51</f>
+        <f t="shared" ref="R51:R70" si="34">AD51*AE51</f>
         <v>300</v>
       </c>
       <c r="S51" s="25"/>
       <c r="T51" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>13.962264150943396</v>
       </c>
       <c r="U51" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8.3018867924528301</v>
       </c>
       <c r="V51" s="1">
@@ -12535,7 +12673,7 @@
       </c>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1">
-        <f t="shared" ref="AC51:AC70" si="34">G51*Q51</f>
+        <f t="shared" ref="AC51:AC70" si="35">G51*Q51</f>
         <v>302</v>
       </c>
       <c r="AD51" s="7">
@@ -12543,11 +12681,11 @@
         <v>5</v>
       </c>
       <c r="AE51" s="9">
-        <f t="shared" ref="AE51:AE68" si="35">MROUND(Q51, AD51*AG51)/AD51</f>
+        <f t="shared" ref="AE51:AE68" si="36">MROUND(Q51, AD51*AG51)/AD51</f>
         <v>60</v>
       </c>
       <c r="AF51" s="1">
-        <f t="shared" ref="AF51:AF68" si="36">AE51*AD51*G51</f>
+        <f t="shared" ref="AF51:AF68" si="37">AE51*AD51*G51</f>
         <v>300</v>
       </c>
       <c r="AG51" s="1">
@@ -12559,10 +12697,13 @@
         <v>144</v>
       </c>
       <c r="AI51" s="9">
-        <f t="shared" ref="AI51:AI70" si="37">AE51/AH51</f>
+        <f t="shared" ref="AI51:AI70" si="38">AE51/AH51</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="AJ51" s="1"/>
+      <c r="AJ51" s="1">
+        <f t="shared" si="6"/>
+        <v>53</v>
+      </c>
       <c r="AK51" s="1"/>
       <c r="AL51" s="1"/>
       <c r="AM51" s="1"/>
@@ -12614,7 +12755,7 @@
         <v>6</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M52" s="1"/>
@@ -12623,23 +12764,23 @@
         <v>0</v>
       </c>
       <c r="P52" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1.2</v>
       </c>
       <c r="Q52" s="5"/>
       <c r="R52" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="S52" s="25"/>
       <c r="T52" s="1">
-        <f t="shared" si="29"/>
-        <v>84.166666666666671</v>
-      </c>
-      <c r="U52" s="1">
         <f t="shared" si="30"/>
         <v>84.166666666666671</v>
       </c>
+      <c r="U52" s="1">
+        <f t="shared" si="31"/>
+        <v>84.166666666666671</v>
+      </c>
       <c r="V52" s="1">
         <v>6.2</v>
       </c>
@@ -12662,7 +12803,7 @@
         <v>113</v>
       </c>
       <c r="AC52" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD52" s="7">
@@ -12670,11 +12811,11 @@
         <v>5</v>
       </c>
       <c r="AE52" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AF52" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AG52" s="1">
@@ -12686,10 +12827,13 @@
         <v>84</v>
       </c>
       <c r="AI52" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AJ52" s="1"/>
+      <c r="AJ52" s="1">
+        <f t="shared" si="6"/>
+        <v>1.2</v>
+      </c>
       <c r="AK52" s="1"/>
       <c r="AL52" s="1"/>
       <c r="AM52" s="1"/>
@@ -12741,7 +12885,7 @@
         <v>167.8</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-6.2000000000000171</v>
       </c>
       <c r="M53" s="1"/>
@@ -12750,24 +12894,24 @@
         <v>103.6</v>
       </c>
       <c r="P53" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>32.32</v>
       </c>
       <c r="Q53" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>170.07999999999998</v>
       </c>
       <c r="R53" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>155.4</v>
       </c>
       <c r="S53" s="25"/>
       <c r="T53" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>13.545792079207919</v>
       </c>
       <c r="U53" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8.7376237623762361</v>
       </c>
       <c r="V53" s="1">
@@ -12790,7 +12934,7 @@
       </c>
       <c r="AB53" s="1"/>
       <c r="AC53" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>170.07999999999998</v>
       </c>
       <c r="AD53" s="7">
@@ -12798,11 +12942,11 @@
         <v>3.7</v>
       </c>
       <c r="AE53" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>42</v>
       </c>
       <c r="AF53" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>155.4</v>
       </c>
       <c r="AG53" s="1">
@@ -12814,10 +12958,13 @@
         <v>126</v>
       </c>
       <c r="AI53" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AJ53" s="1"/>
+      <c r="AJ53" s="1">
+        <f t="shared" si="6"/>
+        <v>32.32</v>
+      </c>
       <c r="AK53" s="1"/>
       <c r="AL53" s="1"/>
       <c r="AM53" s="1"/>
@@ -12868,7 +13015,7 @@
         <v>717</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-499</v>
       </c>
       <c r="M54" s="1"/>
@@ -12877,23 +13024,23 @@
         <v>1764</v>
       </c>
       <c r="P54" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>43.6</v>
       </c>
       <c r="Q54" s="5"/>
       <c r="R54" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="S54" s="25"/>
       <c r="T54" s="1">
-        <f t="shared" si="29"/>
-        <v>40.550458715596328</v>
-      </c>
-      <c r="U54" s="1">
         <f t="shared" si="30"/>
         <v>40.550458715596328</v>
       </c>
+      <c r="U54" s="1">
+        <f t="shared" si="31"/>
+        <v>40.550458715596328</v>
+      </c>
       <c r="V54" s="1">
         <v>120.2</v>
       </c>
@@ -12916,7 +13063,7 @@
         <v>95</v>
       </c>
       <c r="AC54" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD54" s="7">
@@ -12924,11 +13071,11 @@
         <v>6</v>
       </c>
       <c r="AE54" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AF54" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AG54" s="1">
@@ -12940,10 +13087,13 @@
         <v>140</v>
       </c>
       <c r="AI54" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AJ54" s="1"/>
+      <c r="AJ54" s="1">
+        <f t="shared" si="6"/>
+        <v>10.028</v>
+      </c>
       <c r="AK54" s="1"/>
       <c r="AL54" s="1"/>
       <c r="AM54" s="1"/>
@@ -12995,7 +13145,7 @@
         <v>761</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-66</v>
       </c>
       <c r="M55" s="1"/>
@@ -13004,24 +13154,24 @@
         <v>0</v>
       </c>
       <c r="P55" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>139</v>
       </c>
       <c r="Q55" s="5">
-        <f t="shared" ref="Q55:Q56" si="38">$Q$1*P55-O55-F55</f>
+        <f t="shared" ref="Q55:Q56" si="39">$Q$1*P55-O55-F55</f>
         <v>789.7</v>
       </c>
       <c r="R55" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>840</v>
       </c>
       <c r="S55" s="25"/>
       <c r="T55" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>14.661870503597122</v>
       </c>
       <c r="U55" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8.6187050359712227</v>
       </c>
       <c r="V55" s="1">
@@ -13044,7 +13194,7 @@
       </c>
       <c r="AB55" s="1"/>
       <c r="AC55" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>197.42500000000001</v>
       </c>
       <c r="AD55" s="7">
@@ -13052,11 +13202,11 @@
         <v>12</v>
       </c>
       <c r="AE55" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>70</v>
       </c>
       <c r="AF55" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>210</v>
       </c>
       <c r="AG55" s="1">
@@ -13068,10 +13218,13 @@
         <v>70</v>
       </c>
       <c r="AI55" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
-      <c r="AJ55" s="1"/>
+      <c r="AJ55" s="1">
+        <f t="shared" si="6"/>
+        <v>34.75</v>
+      </c>
       <c r="AK55" s="1"/>
       <c r="AL55" s="1"/>
       <c r="AM55" s="1"/>
@@ -13123,7 +13276,7 @@
         <v>651</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-58</v>
       </c>
       <c r="M56" s="1"/>
@@ -13132,24 +13285,24 @@
         <v>840</v>
       </c>
       <c r="P56" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>118.6</v>
       </c>
       <c r="Q56" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>549.98</v>
       </c>
       <c r="R56" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>504</v>
       </c>
       <c r="S56" s="25"/>
       <c r="T56" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>13.91231028667791</v>
       </c>
       <c r="U56" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9.6627318718381119</v>
       </c>
       <c r="V56" s="1">
@@ -13172,7 +13325,7 @@
       </c>
       <c r="AB56" s="1"/>
       <c r="AC56" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>137.495</v>
       </c>
       <c r="AD56" s="7">
@@ -13180,11 +13333,11 @@
         <v>12</v>
       </c>
       <c r="AE56" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>42</v>
       </c>
       <c r="AF56" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>126</v>
       </c>
       <c r="AG56" s="1">
@@ -13196,10 +13349,13 @@
         <v>70</v>
       </c>
       <c r="AI56" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.6</v>
       </c>
-      <c r="AJ56" s="1"/>
+      <c r="AJ56" s="1">
+        <f t="shared" si="6"/>
+        <v>29.65</v>
+      </c>
       <c r="AK56" s="1"/>
       <c r="AL56" s="1"/>
       <c r="AM56" s="1"/>
@@ -13251,7 +13407,7 @@
         <v>324</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-62</v>
       </c>
       <c r="M57" s="1"/>
@@ -13260,24 +13416,24 @@
         <v>0</v>
       </c>
       <c r="P57" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>52.4</v>
       </c>
       <c r="Q57" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>282.60000000000002</v>
       </c>
       <c r="R57" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>252</v>
       </c>
       <c r="S57" s="25"/>
       <c r="T57" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>13.416030534351146</v>
       </c>
       <c r="U57" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8.6068702290076331</v>
       </c>
       <c r="V57" s="1">
@@ -13300,7 +13456,7 @@
       </c>
       <c r="AB57" s="1"/>
       <c r="AC57" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>50.868000000000002</v>
       </c>
       <c r="AD57" s="7">
@@ -13308,11 +13464,11 @@
         <v>6</v>
       </c>
       <c r="AE57" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>42</v>
       </c>
       <c r="AF57" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>45.36</v>
       </c>
       <c r="AG57" s="1">
@@ -13324,10 +13480,13 @@
         <v>140</v>
       </c>
       <c r="AI57" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.3</v>
       </c>
-      <c r="AJ57" s="1"/>
+      <c r="AJ57" s="1">
+        <f t="shared" si="6"/>
+        <v>9.4319999999999986</v>
+      </c>
       <c r="AK57" s="1"/>
       <c r="AL57" s="1"/>
       <c r="AM57" s="1"/>
@@ -13379,7 +13538,7 @@
         <v>283</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-50</v>
       </c>
       <c r="M58" s="1"/>
@@ -13388,23 +13547,23 @@
         <v>336</v>
       </c>
       <c r="P58" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>46.6</v>
       </c>
       <c r="Q58" s="5"/>
       <c r="R58" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="S58" s="25"/>
       <c r="T58" s="1">
-        <f t="shared" si="29"/>
-        <v>14.613733905579398</v>
-      </c>
-      <c r="U58" s="1">
         <f t="shared" si="30"/>
         <v>14.613733905579398</v>
       </c>
+      <c r="U58" s="1">
+        <f t="shared" si="31"/>
+        <v>14.613733905579398</v>
+      </c>
       <c r="V58" s="1">
         <v>66.2</v>
       </c>
@@ -13425,7 +13584,7 @@
       </c>
       <c r="AB58" s="1"/>
       <c r="AC58" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD58" s="7">
@@ -13433,11 +13592,11 @@
         <v>6</v>
       </c>
       <c r="AE58" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AF58" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AG58" s="1">
@@ -13449,10 +13608,13 @@
         <v>140</v>
       </c>
       <c r="AI58" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AJ58" s="1"/>
+      <c r="AJ58" s="1">
+        <f t="shared" si="6"/>
+        <v>8.3879999999999999</v>
+      </c>
       <c r="AK58" s="1"/>
       <c r="AL58" s="1"/>
       <c r="AM58" s="1"/>
@@ -13504,7 +13666,7 @@
         <v>10</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M59" s="1"/>
@@ -13513,23 +13675,23 @@
         <v>0</v>
       </c>
       <c r="P59" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2</v>
       </c>
       <c r="Q59" s="5"/>
       <c r="R59" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="S59" s="25"/>
       <c r="T59" s="1">
-        <f t="shared" si="29"/>
-        <v>24.5</v>
-      </c>
-      <c r="U59" s="1">
         <f t="shared" si="30"/>
         <v>24.5</v>
       </c>
+      <c r="U59" s="1">
+        <f t="shared" si="31"/>
+        <v>24.5</v>
+      </c>
       <c r="V59" s="1">
         <v>2.2000000000000002</v>
       </c>
@@ -13552,7 +13714,7 @@
         <v>90</v>
       </c>
       <c r="AC59" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD59" s="7">
@@ -13560,11 +13722,11 @@
         <v>6</v>
       </c>
       <c r="AE59" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AF59" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AG59" s="1">
@@ -13576,10 +13738,13 @@
         <v>140</v>
       </c>
       <c r="AI59" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AJ59" s="1"/>
+      <c r="AJ59" s="1">
+        <f t="shared" si="6"/>
+        <v>0.36</v>
+      </c>
       <c r="AK59" s="1"/>
       <c r="AL59" s="1"/>
       <c r="AM59" s="1"/>
@@ -13631,7 +13796,7 @@
         <v>901</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-93</v>
       </c>
       <c r="M60" s="1"/>
@@ -13640,24 +13805,24 @@
         <v>840</v>
       </c>
       <c r="P60" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>161.6</v>
       </c>
       <c r="Q60" s="5">
-        <f t="shared" ref="Q60:Q61" si="39">$Q$1*P60-O60-F60</f>
+        <f t="shared" ref="Q60:Q61" si="40">$Q$1*P60-O60-F60</f>
         <v>850.88000000000011</v>
       </c>
       <c r="R60" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>840</v>
       </c>
       <c r="S60" s="25"/>
       <c r="T60" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>14.232673267326733</v>
       </c>
       <c r="U60" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9.0346534653465351</v>
       </c>
       <c r="V60" s="1">
@@ -13680,7 +13845,7 @@
       </c>
       <c r="AB60" s="1"/>
       <c r="AC60" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>255.26400000000001</v>
       </c>
       <c r="AD60" s="7">
@@ -13688,11 +13853,11 @@
         <v>12</v>
       </c>
       <c r="AE60" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>70</v>
       </c>
       <c r="AF60" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>252</v>
       </c>
       <c r="AG60" s="1">
@@ -13704,10 +13869,13 @@
         <v>70</v>
       </c>
       <c r="AI60" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
-      <c r="AJ60" s="1"/>
+      <c r="AJ60" s="1">
+        <f t="shared" si="6"/>
+        <v>48.48</v>
+      </c>
       <c r="AK60" s="1"/>
       <c r="AL60" s="1"/>
       <c r="AM60" s="1"/>
@@ -13759,7 +13927,7 @@
         <v>667</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-94</v>
       </c>
       <c r="M61" s="1"/>
@@ -13768,24 +13936,24 @@
         <v>504</v>
       </c>
       <c r="P61" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>114.6</v>
       </c>
       <c r="Q61" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>687.78</v>
       </c>
       <c r="R61" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>672</v>
       </c>
       <c r="S61" s="25"/>
       <c r="T61" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>14.162303664921467</v>
       </c>
       <c r="U61" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8.2984293193717278</v>
       </c>
       <c r="V61" s="1">
@@ -13808,7 +13976,7 @@
       </c>
       <c r="AB61" s="1"/>
       <c r="AC61" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>206.33399999999997</v>
       </c>
       <c r="AD61" s="7">
@@ -13816,11 +13984,11 @@
         <v>12</v>
       </c>
       <c r="AE61" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>56</v>
       </c>
       <c r="AF61" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>201.6</v>
       </c>
       <c r="AG61" s="1">
@@ -13832,10 +14000,13 @@
         <v>70</v>
       </c>
       <c r="AI61" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.8</v>
       </c>
-      <c r="AJ61" s="1"/>
+      <c r="AJ61" s="1">
+        <f t="shared" si="6"/>
+        <v>34.379999999999995</v>
+      </c>
       <c r="AK61" s="1"/>
       <c r="AL61" s="1"/>
       <c r="AM61" s="1"/>
@@ -13887,7 +14058,7 @@
         <v>541</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-66</v>
       </c>
       <c r="M62" s="1"/>
@@ -13896,24 +14067,24 @@
         <v>784</v>
       </c>
       <c r="P62" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>95</v>
       </c>
       <c r="Q62" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>221</v>
       </c>
       <c r="R62" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>196</v>
       </c>
       <c r="S62" s="25"/>
       <c r="T62" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>13.736842105263158</v>
       </c>
       <c r="U62" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>11.673684210526316</v>
       </c>
       <c r="V62" s="1">
@@ -13936,7 +14107,7 @@
       </c>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>66.3</v>
       </c>
       <c r="AD62" s="7">
@@ -13944,11 +14115,11 @@
         <v>14</v>
       </c>
       <c r="AE62" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>14</v>
       </c>
       <c r="AF62" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>58.8</v>
       </c>
       <c r="AG62" s="1">
@@ -13960,10 +14131,13 @@
         <v>70</v>
       </c>
       <c r="AI62" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.2</v>
       </c>
-      <c r="AJ62" s="1"/>
+      <c r="AJ62" s="1">
+        <f t="shared" si="6"/>
+        <v>28.5</v>
+      </c>
       <c r="AK62" s="1"/>
       <c r="AL62" s="1"/>
       <c r="AM62" s="1"/>
@@ -14014,7 +14188,7 @@
         <v>1309</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-230</v>
       </c>
       <c r="M63" s="1"/>
@@ -14023,23 +14197,23 @@
         <v>2520</v>
       </c>
       <c r="P63" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>215.8</v>
       </c>
       <c r="Q63" s="5"/>
       <c r="R63" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="S63" s="25"/>
       <c r="T63" s="1">
-        <f t="shared" si="29"/>
-        <v>18.382761816496757</v>
-      </c>
-      <c r="U63" s="1">
         <f t="shared" si="30"/>
         <v>18.382761816496757</v>
       </c>
+      <c r="U63" s="1">
+        <f t="shared" si="31"/>
+        <v>18.382761816496757</v>
+      </c>
       <c r="V63" s="1">
         <v>216.4</v>
       </c>
@@ -14062,7 +14236,7 @@
         <v>69</v>
       </c>
       <c r="AC63" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD63" s="7">
@@ -14070,11 +14244,11 @@
         <v>12</v>
       </c>
       <c r="AE63" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AF63" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AG63" s="1">
@@ -14086,10 +14260,13 @@
         <v>70</v>
       </c>
       <c r="AI63" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AJ63" s="1"/>
+      <c r="AJ63" s="1">
+        <f t="shared" si="6"/>
+        <v>53.95</v>
+      </c>
       <c r="AK63" s="1"/>
       <c r="AL63" s="1"/>
       <c r="AM63" s="1"/>
@@ -14143,7 +14320,7 @@
         <v>1438</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-180</v>
       </c>
       <c r="M64" s="1"/>
@@ -14152,7 +14329,7 @@
         <v>0</v>
       </c>
       <c r="P64" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>251.6</v>
       </c>
       <c r="Q64" s="5">
@@ -14160,16 +14337,16 @@
         <v>1317.88</v>
       </c>
       <c r="R64" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1344</v>
       </c>
       <c r="S64" s="25"/>
       <c r="T64" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>14.403815580286169</v>
       </c>
       <c r="U64" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9.0620031796502385</v>
       </c>
       <c r="V64" s="1">
@@ -14192,7 +14369,7 @@
       </c>
       <c r="AB64" s="1"/>
       <c r="AC64" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>329.47</v>
       </c>
       <c r="AD64" s="7">
@@ -14200,11 +14377,11 @@
         <v>12</v>
       </c>
       <c r="AE64" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>112</v>
       </c>
       <c r="AF64" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>336</v>
       </c>
       <c r="AG64" s="1">
@@ -14216,10 +14393,13 @@
         <v>70</v>
       </c>
       <c r="AI64" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1.6</v>
       </c>
-      <c r="AJ64" s="1"/>
+      <c r="AJ64" s="1">
+        <f t="shared" si="6"/>
+        <v>62.9</v>
+      </c>
       <c r="AK64" s="1"/>
       <c r="AL64" s="1"/>
       <c r="AM64" s="1"/>
@@ -14271,7 +14451,7 @@
         <v>641</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-212</v>
       </c>
       <c r="M65" s="1"/>
@@ -14280,24 +14460,24 @@
         <v>588</v>
       </c>
       <c r="P65" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>85.8</v>
       </c>
       <c r="Q65" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>597.20000000000005</v>
       </c>
       <c r="R65" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>588</v>
       </c>
       <c r="S65" s="25"/>
       <c r="T65" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>13.892773892773894</v>
       </c>
       <c r="U65" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>7.0396270396270397</v>
       </c>
       <c r="V65" s="1">
@@ -14320,7 +14500,7 @@
       </c>
       <c r="AB65" s="1"/>
       <c r="AC65" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>119.44000000000001</v>
       </c>
       <c r="AD65" s="7">
@@ -14328,11 +14508,11 @@
         <v>6</v>
       </c>
       <c r="AE65" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>98</v>
       </c>
       <c r="AF65" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>117.60000000000001</v>
       </c>
       <c r="AG65" s="1">
@@ -14344,10 +14524,13 @@
         <v>140</v>
       </c>
       <c r="AI65" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.7</v>
       </c>
-      <c r="AJ65" s="1"/>
+      <c r="AJ65" s="1">
+        <f t="shared" si="6"/>
+        <v>17.16</v>
+      </c>
       <c r="AK65" s="1"/>
       <c r="AL65" s="1"/>
       <c r="AM65" s="1"/>
@@ -14399,7 +14582,7 @@
         <v>829</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-90</v>
       </c>
       <c r="M66" s="1"/>
@@ -14408,7 +14591,7 @@
         <v>1680</v>
       </c>
       <c r="P66" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>147.80000000000001</v>
       </c>
       <c r="Q66" s="5">
@@ -14416,16 +14599,16 @@
         <v>248.54000000000042</v>
       </c>
       <c r="R66" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>252</v>
       </c>
       <c r="S66" s="25"/>
       <c r="T66" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>14.323410013531799</v>
       </c>
       <c r="U66" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>12.618403247631933</v>
       </c>
       <c r="V66" s="1">
@@ -14448,7 +14631,7 @@
       </c>
       <c r="AB66" s="1"/>
       <c r="AC66" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>57.1642000000001</v>
       </c>
       <c r="AD66" s="7">
@@ -14456,11 +14639,11 @@
         <v>6</v>
       </c>
       <c r="AE66" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>42</v>
       </c>
       <c r="AF66" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>57.96</v>
       </c>
       <c r="AG66" s="1">
@@ -14472,10 +14655,13 @@
         <v>140</v>
       </c>
       <c r="AI66" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.3</v>
       </c>
-      <c r="AJ66" s="1"/>
+      <c r="AJ66" s="1">
+        <f t="shared" si="6"/>
+        <v>33.994000000000007</v>
+      </c>
       <c r="AK66" s="1"/>
       <c r="AL66" s="1"/>
       <c r="AM66" s="1"/>
@@ -14527,7 +14713,7 @@
         <v>39.799999999999997</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-1.8999999999999986</v>
       </c>
       <c r="M67" s="1"/>
@@ -14536,24 +14722,24 @@
         <v>37.799999999999997</v>
       </c>
       <c r="P67" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>7.58</v>
       </c>
       <c r="Q67" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>38.720000000000006</v>
       </c>
       <c r="R67" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>37.800000000000004</v>
       </c>
       <c r="S67" s="25"/>
       <c r="T67" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>13.878627968337733</v>
       </c>
       <c r="U67" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8.8918205804749348</v>
       </c>
       <c r="V67" s="1">
@@ -14576,7 +14762,7 @@
       </c>
       <c r="AB67" s="1"/>
       <c r="AC67" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>38.720000000000006</v>
       </c>
       <c r="AD67" s="7">
@@ -14584,11 +14770,11 @@
         <v>2.7</v>
       </c>
       <c r="AE67" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>14</v>
       </c>
       <c r="AF67" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>37.800000000000004</v>
       </c>
       <c r="AG67" s="1">
@@ -14600,10 +14786,13 @@
         <v>126</v>
       </c>
       <c r="AI67" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="AJ67" s="1"/>
+      <c r="AJ67" s="1">
+        <f t="shared" si="6"/>
+        <v>7.58</v>
+      </c>
       <c r="AK67" s="1"/>
       <c r="AL67" s="1"/>
       <c r="AM67" s="1"/>
@@ -14657,7 +14846,7 @@
         <v>235</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>125</v>
       </c>
       <c r="M68" s="1"/>
@@ -14666,24 +14855,24 @@
         <v>240</v>
       </c>
       <c r="P68" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>72</v>
       </c>
       <c r="Q68" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>393</v>
       </c>
       <c r="R68" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>420</v>
       </c>
       <c r="S68" s="25"/>
       <c r="T68" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>14.375</v>
       </c>
       <c r="U68" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8.5416666666666661</v>
       </c>
       <c r="V68" s="1">
@@ -14706,7 +14895,7 @@
       </c>
       <c r="AB68" s="1"/>
       <c r="AC68" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>393</v>
       </c>
       <c r="AD68" s="7">
@@ -14714,11 +14903,11 @@
         <v>5</v>
       </c>
       <c r="AE68" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>84</v>
       </c>
       <c r="AF68" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>420</v>
       </c>
       <c r="AG68" s="1">
@@ -14730,10 +14919,13 @@
         <v>84</v>
       </c>
       <c r="AI68" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
-      <c r="AJ68" s="1"/>
+      <c r="AJ68" s="1">
+        <f t="shared" si="6"/>
+        <v>72</v>
+      </c>
       <c r="AK68" s="1"/>
       <c r="AL68" s="1"/>
       <c r="AM68" s="1"/>
@@ -14783,25 +14975,25 @@
         <v>145</v>
       </c>
       <c r="L69" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-10</v>
       </c>
       <c r="M69" s="13"/>
       <c r="N69" s="13"/>
       <c r="O69" s="13"/>
       <c r="P69" s="13">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>27</v>
       </c>
       <c r="Q69" s="15"/>
       <c r="R69" s="15"/>
       <c r="S69" s="24"/>
       <c r="T69" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2.8777777777777778</v>
       </c>
       <c r="U69" s="13">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>2.8777777777777778</v>
       </c>
       <c r="V69" s="13">
@@ -14830,7 +15022,10 @@
       <c r="AG69" s="13"/>
       <c r="AH69" s="13"/>
       <c r="AI69" s="16"/>
-      <c r="AJ69" s="1"/>
+      <c r="AJ69" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AK69" s="1"/>
       <c r="AL69" s="1"/>
       <c r="AM69" s="1"/>
@@ -14875,7 +15070,7 @@
         <v>300</v>
       </c>
       <c r="R70" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>288</v>
       </c>
       <c r="S70" s="25"/>
@@ -14901,18 +15096,18 @@
       </c>
       <c r="AB70" s="1"/>
       <c r="AC70" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>240</v>
       </c>
       <c r="AD70" s="7">
         <v>8</v>
       </c>
       <c r="AE70" s="9">
-        <f t="shared" ref="AE70" si="40">MROUND(Q70, AD70*AG70)/AD70</f>
+        <f t="shared" ref="AE70" si="41">MROUND(Q70, AD70*AG70)/AD70</f>
         <v>36</v>
       </c>
       <c r="AF70" s="1">
-        <f t="shared" ref="AF70" si="41">AE70*AD70*G70</f>
+        <f t="shared" ref="AF70" si="42">AE70*AD70*G70</f>
         <v>230.4</v>
       </c>
       <c r="AG70" s="1">
@@ -14922,7 +15117,7 @@
         <v>84</v>
       </c>
       <c r="AI70" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="AJ70" s="1"/>
